--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Priyasha Shah</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9861494544</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9861494544</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9861494544</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9861494544</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.67509</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.67509</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -948,25 +942,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.34637</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.34636999999999</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1015,7 +1005,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1306,7 +1296,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,42 +494,42 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -982,6 +982,213 @@
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 9:52 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367040</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Deepak Babu Bhatta</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Deepak Babu Bhatta</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9860985865</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 09:52:59 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860985865</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:30:34 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 09:52:59 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Radha Krishna Temple, Raniban - Hindu temple P7JP+2X5 Radha Krishna Chowk, Yerahity Raniban Rd Nagar</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>9860985865@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>CDB647</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 14h 22m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -996,16 +1203,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1033,7 +1240,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1043,7 +1250,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1078,7 +1285,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 19m</t>
+          <t>1d 7h 21m</t>
         </is>
       </c>
     </row>
@@ -1130,203 +1337,311 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1367391</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Priyasha Shah</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>13 Oct 2026 09:28:39 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 09:09:03 AM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>13 Oct 2026 09:28:39 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>1d 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367040</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Deepak Babu Bhatta</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 09:52:59 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:30:34 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 09:52:59 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>1d 14h 22m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -483,18 +483,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -510,14 +510,14 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -534,7 +534,7 @@
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1052,10 +1052,8 @@
           <t>Deepak Babu Bhatta</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9860985865</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9860985865</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1127,10 +1125,8 @@
           <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH3" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
@@ -1149,10 +1145,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1163,32 +1157,665 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 14h 22m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:18 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368046</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Sarishma Ranjitkar</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Sarishma Ranjitkar</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9843906185</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:18:26 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9843906185</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 04:03:08 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:18:26 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.67491</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Near Bholachhen Pond, Bhaktapur Durbar Square, Bhaktapur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>sarishmaranjitkar17@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>04:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L37-2</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.431547</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>1d 14h 22m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>18h 15m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:23 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367816</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Chaulagain</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Chaulagain</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9813974696</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9813974696</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:23:25 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.707462</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>near Asan Bazar Chittadhar Marg, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>sc321388@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>07:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.312359</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:22 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367816</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Chaulagain</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Chaulagain</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9813974696</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9813974696</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:23:25 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.707462</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>near Asan Bazar Chittadhar Marg, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>sc321388@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>07:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.312359</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1240,7 +1867,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1250,7 +1877,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1273,7 +1900,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>8h 32m</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1912,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 7h 21m</t>
+          <t>1d 43m</t>
         </is>
       </c>
     </row>
@@ -1326,10 +1953,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1402,10 +2029,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -1611,14 +2238,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>13 Oct 2026 09:52:59 AM</t>
@@ -1642,6 +2269,207 @@
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>1d 14h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368046</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Sarishma Ranjitkar</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:18:26 AM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 04:03:08 PM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:18:26 AM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>18h 15m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367816</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Sabin Chaulagain</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:23:25 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367816</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Chaulagain</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:23:25 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1253,10 +1253,8 @@
           <t>Sarishma Ranjitkar</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9843906185</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9843906185</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1291,10 +1289,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.67491</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.67491</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1350,25 +1346,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L37-2</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.431547</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.43154699999999</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1464,10 +1456,8 @@
           <t>Sabin Chaulagain</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9813974696</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9813974696</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1502,10 +1492,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.707462</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.707462</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1561,25 +1549,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.312359</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.312359</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1675,10 +1659,8 @@
           <t>Sabin Chaulagain</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9813974696</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9813974696</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1713,10 +1695,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.707462</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.707462</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1772,50 +1752,468 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.312359</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.312359</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>21h 20m</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>21h 20m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368040</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Hitesh Bajracharya</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Hitesh Bajracharya</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9840302981</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9840302981</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:59:00 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.6736</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Purnachandi Temple,Gabahal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>bajrahitesh06@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>04:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.32107</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>18h 38m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:46 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367937</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Khadgi</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Khadgi</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9818239508</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:34:15 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9841385645</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:34:15 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:46:41 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.70844</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>27.70843, 85.31185 Tyoda Asan, Kathmandu  , ASAN tyoda ,Kathmandu Metropolitan ward- 25 , Kathmandu,</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>deepeshgai@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>06:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.31179</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1830,7 +2228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1867,7 +2265,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1877,7 +2275,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -1900,7 +2298,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 32m</t>
+          <t>8h 59m</t>
         </is>
       </c>
     </row>
@@ -1912,7 +2310,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 43m</t>
+          <t>23h 12m</t>
         </is>
       </c>
     </row>
@@ -1953,10 +2351,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -2029,10 +2427,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -2305,7 +2703,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2372,7 +2770,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2439,14 +2837,14 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 01:02:31 PM</t>
@@ -2470,6 +2868,140 @@
       <c r="M24" s="3" t="inlineStr">
         <is>
           <t>21h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1368040</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Hitesh Bajracharya</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:59:00 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>18h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367937</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Khadgi</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:34:15 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:34:15 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:46:41 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1862,10 +1862,8 @@
           <t>Hitesh Bajracharya</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9840302981</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9840302981</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1900,10 +1898,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.6736</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.6736</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1959,25 +1955,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>4,3</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.32107</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.32107000000001</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2063,20 +2055,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Dipesh Khadgi</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9818239508</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9818239508</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2111,10 +2097,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.70844</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.70844</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2170,25 +2154,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>3,8</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.31179</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.31179</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2237,7 +2217,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2904,7 +2884,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2971,7 +2951,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -2194,6 +2194,217 @@
       <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:04 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Iptv</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367977</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Rajip Maharjan</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Rajip Maharjan</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9841612262</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:04:22 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9861758066</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:05:00 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:04:22 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.67494</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Next to Bhatti Restro, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>razzeep@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>05:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.31944</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -2208,16 +2419,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2245,7 +2456,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2255,7 +2466,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2278,7 +2489,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 59m</t>
+          <t>7h 51m</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2501,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 12m</t>
+          <t>22h 48m</t>
         </is>
       </c>
     </row>
@@ -2349,10 +2560,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -2441,167 +2652,123 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1367391</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Priyasha Shah</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:28:39 AM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 09:09:03 AM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:28:39 AM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>1d 19m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TKT1367040</t>
+          <t>TKT1367391</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Deepak Babu Bhatta</t>
+          <t>Priyasha Shah</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2621,22 +2788,22 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 09:52:59 AM</t>
+          <t>13 Oct 2026 09:28:39 AM</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:30:34 PM</t>
+          <t>12 Oct 2026 09:09:03 AM</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 09:52:59 AM</t>
+          <t>13 Oct 2026 09:28:39 AM</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -2646,29 +2813,29 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>1d 14h 22m</t>
+          <t>1d 19m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>TKT1368046</t>
+          <t>TKT1367040</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sarishma Ranjitkar</t>
+          <t>Deepak Babu Bhatta</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2688,22 +2855,22 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:18:26 AM</t>
+          <t>13 Oct 2026 09:52:59 AM</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 04:03:08 PM</t>
+          <t>11 Oct 2026 07:30:34 PM</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:18:26 AM</t>
+          <t>13 Oct 2026 09:52:59 AM</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2713,19 +2880,19 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>18h 15m</t>
+          <t>1d 14h 22m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1367816</t>
+          <t>TKT1368046</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Sabin Chaulagain</t>
+          <t>Sarishma Ranjitkar</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2740,12 +2907,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2755,32 +2922,32 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>13 Oct 2026 10:18:26 AM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>12 Oct 2026 04:03:08 PM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:23:25 AM</t>
+          <t>13 Oct 2026 10:18:26 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>18h 15m</t>
         </is>
       </c>
     </row>
@@ -2854,12 +3021,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1368040</t>
+          <t>TKT1367816</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Hitesh Bajracharya</t>
+          <t>Sabin Chaulagain</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2874,12 +3041,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2889,99 +3056,233 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:37:39 AM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 03:59:00 PM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:37:39 AM</t>
+          <t>13 Oct 2026 10:23:25 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 20m</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>18h 38m</t>
+          <t>21h 20m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>TKT1368040</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Hitesh Bajracharya</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:59:00 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>18h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>TKT1367937</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Dipesh Khadgi</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026 02:34:15 PM</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026 02:34:15 PM</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>13 Oct 2026 10:46:41 AM</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>20h 12m</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>20h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367977</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Rajip Maharjan</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:04:22 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:05:00 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:04:22 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="28" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -2264,10 +2264,8 @@
           <t>Rajip Maharjan</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9841612262</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9841612262</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2302,10 +2300,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.67494</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.67494</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2361,48 +2357,147 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.31944</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.31944</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>19h 59m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:22 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr"/>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr"/>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
         </is>
@@ -2419,7 +2514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2428,7 +2523,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2456,7 +2551,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2477,7 +2572,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -2571,80 +2666,71 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -2660,7 +2746,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -2675,224 +2761,128 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1367391</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Priyasha Shah</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:28:39 AM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 09:09:03 AM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:28:39 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>1d 19m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1367040</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Deepak Babu Bhatta</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>NETTV-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:52:59 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:30:34 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:52:59 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>1d 14h 22m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1368046</t>
+          <t>TKT1367391</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Sarishma Ranjitkar</t>
+          <t>Priyasha Shah</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2922,22 +2912,22 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:18:26 AM</t>
+          <t>13 Oct 2026 09:28:39 AM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 04:03:08 PM</t>
+          <t>12 Oct 2026 09:09:03 AM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:18:26 AM</t>
+          <t>13 Oct 2026 09:28:39 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2947,39 +2937,39 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>18h 15m</t>
+          <t>1d 19m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1367816</t>
+          <t>TKT1367040</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Sabin Chaulagain</t>
+          <t>Deepak Babu Bhatta</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2989,44 +2979,44 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>13 Oct 2026 09:52:59 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>11 Oct 2026 07:30:34 PM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:23:25 AM</t>
+          <t>13 Oct 2026 09:52:59 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>1d 14h 22m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1367816</t>
+          <t>TKT1368046</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Sabin Chaulagain</t>
+          <t>Sarishma Ranjitkar</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3041,12 +3031,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -3056,44 +3046,44 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>13 Oct 2026 10:18:26 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>12 Oct 2026 04:03:08 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:23:25 AM</t>
+          <t>13 Oct 2026 10:18:26 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>18h 15m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1368040</t>
+          <t>TKT1367816</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Hitesh Bajracharya</t>
+          <t>Sabin Chaulagain</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3108,12 +3098,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3123,44 +3113,44 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:37:39 AM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 03:59:00 PM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:37:39 AM</t>
+          <t>13 Oct 2026 10:23:25 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 20m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>18h 38m</t>
+          <t>21h 20m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1367937</t>
+          <t>TKT1367816</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Dipesh Khadgi</t>
+          <t>Sabin Chaulagain</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3190,97 +3180,231 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 02:34:15 PM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 02:34:15 PM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:46:41 AM</t>
+          <t>13 Oct 2026 10:23:25 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>21h 20m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>21h 20m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>TKT1368040</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Hitesh Bajracharya</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:59:00 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>18h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367937</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Dipesh Khadgi</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:34:15 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:34:15 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:46:41 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>TKT1367977</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Rajip Maharjan</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>13 Oct 2026 11:04:22 AM</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 03:05:00 PM</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>13 Oct 2026 11:04:22 AM</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>19h 59m</t>
         </is>

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -2503,6 +2503,217 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:46 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367964</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Maharjan</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Maharjan</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9802100124</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:46:47 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9802100124</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:56:06 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:46:47 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.670745</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Chapat Ganesh Marg, Lalitpur 44600 Near by Patan Sundhara, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>nirazonline@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>06:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L112-6</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.32886</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>20h 50m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2514,16 +2725,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2551,7 +2762,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2561,7 +2772,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2572,7 +2783,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2795,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 51m</t>
+          <t>6h 59m</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2807,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 48m</t>
+          <t>22h 35m</t>
         </is>
       </c>
     </row>
@@ -2651,109 +2862,104 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="3" t="n">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -2764,12 +2970,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -2785,238 +2991,150 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1367391</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Priyasha Shah</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:28:39 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 09:09:03 AM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:28:39 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>1d 19m</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1367040</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Deepak Babu Bhatta</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>NETTV-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:52:59 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:30:34 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:52:59 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>1d 14h 22m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1368046</t>
+          <t>TKT1367391</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Sarishma Ranjitkar</t>
+          <t>Priyasha Shah</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3046,22 +3164,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:18:26 AM</t>
+          <t>13 Oct 2026 09:28:39 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 04:03:08 PM</t>
+          <t>12 Oct 2026 09:09:03 AM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:18:26 AM</t>
+          <t>13 Oct 2026 09:28:39 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -3071,39 +3189,39 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>18h 15m</t>
+          <t>1d 19m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1367816</t>
+          <t>TKT1367040</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Sabin Chaulagain</t>
+          <t>Deepak Babu Bhatta</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3113,44 +3231,44 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>13 Oct 2026 09:52:59 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>11 Oct 2026 07:30:34 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:23:25 AM</t>
+          <t>13 Oct 2026 09:52:59 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>1d 14h 22m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1367816</t>
+          <t>TKT1368046</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Sabin Chaulagain</t>
+          <t>Sarishma Ranjitkar</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3165,12 +3283,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3180,44 +3298,44 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>13 Oct 2026 10:18:26 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>12 Oct 2026 04:03:08 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:23:25 AM</t>
+          <t>13 Oct 2026 10:18:26 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>18h 15m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1368040</t>
+          <t>TKT1367816</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Hitesh Bajracharya</t>
+          <t>Sabin Chaulagain</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3232,12 +3350,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3247,44 +3365,44 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:37:39 AM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 03:59:00 PM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:37:39 AM</t>
+          <t>13 Oct 2026 10:23:25 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 20m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>18h 38m</t>
+          <t>21h 20m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1367937</t>
+          <t>TKT1367816</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Dipesh Khadgi</t>
+          <t>Sabin Chaulagain</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3314,99 +3432,300 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 02:34:15 PM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 02:34:15 PM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:46:41 AM</t>
+          <t>13 Oct 2026 10:23:25 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>21h 20m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>21h 20m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>TKT1368040</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Hitesh Bajracharya</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:59:00 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>18h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367937</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Dipesh Khadgi</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:34:15 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:34:15 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:46:41 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>TKT1367977</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Rajip Maharjan</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>13 Oct 2026 11:04:22 AM</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 03:05:00 PM</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>13 Oct 2026 11:04:22 AM</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>19h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367964</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Niraj Maharjan</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:46:47 AM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:56:06 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:46:47 AM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>20h 50m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -2570,10 +2570,8 @@
           <t>Niraj Maharjan</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9802100124</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9802100124</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2608,10 +2606,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.670745</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.670745</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2667,25 +2663,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L112-6</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.32886</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.32886000000001</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2734,7 +2726,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3695,7 +3687,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -2706,6 +2706,209 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 12:28 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367954</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Namrata Deshar</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Namrata Deshar</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9823711114</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 12:28:34 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>LTP9823711114</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:48:22 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 12:28:34 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>B&amp;B Hospital, Gwarko (Baidya &amp; Banskota) - General hospital Lalitpur 44700, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>9866438710@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>07:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB959</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>21h 40m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2717,7 +2920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2726,7 +2929,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2754,7 +2957,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2764,7 +2967,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2775,7 +2978,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2990,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 59m</t>
+          <t>6h 17m</t>
         </is>
       </c>
     </row>
@@ -2799,7 +3002,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 35m</t>
+          <t>22h 30m</t>
         </is>
       </c>
     </row>
@@ -2840,10 +3043,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -2948,10 +3151,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -3721,6 +3924,73 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367954</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Namrata Deshar</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 12:28:34 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:48:22 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 12:28:34 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>21h 40m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -2773,10 +2773,8 @@
           <t>Namrata Deshar</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9823711114</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9823711114</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2866,10 +2864,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
@@ -2880,7 +2876,7 @@
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -2929,7 +2925,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3957,7 +3953,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,12 +494,12 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -2905,6 +2905,842 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 1:16 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367965</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Gautam</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Gautam</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9801093335</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9801093335</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:56:18 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.73129</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Radha Krishna Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>gshankarbro@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>08:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>CDB382</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.28849</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>22h 19m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 1:13 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367965</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Gautam</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Gautam</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9801093335</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9801093335</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:56:18 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.73129</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Radha Krishna Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>gshankarbro@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>08:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB382</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.28849</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>22h 19m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 1:11 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet connection   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>no internet connection</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366305</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9849670860</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:11:41 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>LTP9849670860</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:57:34 AM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:11:41 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Dhobighat, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>info@megahospital.com.np</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>13:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet connection   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 14m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet connection   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 1:10 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>No internet connection</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366302</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital Pharmacy</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital Pharmacy</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9862483865</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:10:44 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>LTP9862483865</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:55:22 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:10:44 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Dhobighat , Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>Megapharmacy@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>13:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 15m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2916,7 +3752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2925,7 +3761,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2953,7 +3789,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2963,7 +3799,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -2974,7 +3810,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>93.3%</t>
         </is>
       </c>
     </row>
@@ -2986,7 +3822,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 17m</t>
+          <t>4h 29m</t>
         </is>
       </c>
     </row>
@@ -2998,7 +3834,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 30m</t>
+          <t>1d 2h 26m</t>
         </is>
       </c>
     </row>
@@ -3039,10 +3875,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -3087,93 +3923,88 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -3184,12 +4015,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -3212,7 +4043,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -3228,238 +4059,150 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1367391</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Priyasha Shah</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:28:39 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 09:09:03 AM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:28:39 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>1d 19m</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1367040</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Deepak Babu Bhatta</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>NETTV-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:52:59 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:30:34 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>13 Oct 2026 09:52:59 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>1d 14h 22m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1368046</t>
+          <t>TKT1367391</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Sarishma Ranjitkar</t>
+          <t>Priyasha Shah</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3489,22 +4232,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:18:26 AM</t>
+          <t>13 Oct 2026 09:28:39 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 04:03:08 PM</t>
+          <t>12 Oct 2026 09:09:03 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:18:26 AM</t>
+          <t>13 Oct 2026 09:28:39 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -3514,39 +4257,39 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>18h 15m</t>
+          <t>1d 19m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1367816</t>
+          <t>TKT1367040</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Sabin Chaulagain</t>
+          <t>Deepak Babu Bhatta</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3556,44 +4299,44 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>13 Oct 2026 09:52:59 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>11 Oct 2026 07:30:34 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:23:25 AM</t>
+          <t>13 Oct 2026 09:52:59 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>1d 14h 22m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1367816</t>
+          <t>TKT1368046</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Sabin Chaulagain</t>
+          <t>Sarishma Ranjitkar</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3608,12 +4351,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3623,44 +4366,44 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>13 Oct 2026 10:18:26 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 01:02:31 PM</t>
+          <t>12 Oct 2026 04:03:08 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:23:25 AM</t>
+          <t>13 Oct 2026 10:18:26 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>21h 20m</t>
+          <t>18h 15m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1368040</t>
+          <t>TKT1367816</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Hitesh Bajracharya</t>
+          <t>Sabin Chaulagain</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3675,12 +4418,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3690,44 +4433,44 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:37:39 AM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 03:59:00 PM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:37:39 AM</t>
+          <t>13 Oct 2026 10:23:25 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 20m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>18h 38m</t>
+          <t>21h 20m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1367937</t>
+          <t>TKT1367816</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Dipesh Khadgi</t>
+          <t>Sabin Chaulagain</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3757,54 +4500,54 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 02:34:15 PM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 02:34:15 PM</t>
+          <t>12 Oct 2026 01:02:31 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 10:46:41 AM</t>
+          <t>13 Oct 2026 10:23:25 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>21h 20m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>21h 20m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1367977</t>
+          <t>TKT1368040</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Rajip Maharjan</t>
+          <t>Hitesh Bajracharya</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -3824,22 +4567,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 11:04:22 AM</t>
+          <t>13 Oct 2026 10:37:39 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 03:05:00 PM</t>
+          <t>12 Oct 2026 03:59:00 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 11:04:22 AM</t>
+          <t>13 Oct 2026 10:37:39 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -3849,39 +4592,39 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>19h 59m</t>
+          <t>18h 38m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1367964</t>
+          <t>TKT1367937</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Niraj Maharjan</t>
+          <t>Dipesh Khadgi</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3891,99 +4634,501 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 11:46:47 AM</t>
+          <t>12 Oct 2026 02:34:15 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 02:56:06 PM</t>
+          <t>12 Oct 2026 02:34:15 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 11:46:47 AM</t>
+          <t>13 Oct 2026 10:46:41 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>20h 50m</t>
+          <t>20h 12m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>TKT1367977</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Rajip Maharjan</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:04:22 AM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:05:00 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:04:22 AM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367964</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Niraj Maharjan</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:46:47 AM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:56:06 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:46:47 AM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>20h 50m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>TKT1367954</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Namrata Deshar</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>13 Oct 2026 12:28:34 PM</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 02:48:22 PM</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>13 Oct 2026 12:28:34 PM</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t>21h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367965</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Shankar Gautam</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:56:18 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>22h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367965</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Gautam</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:56:18 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>22h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1366305</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Mega Hospital</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : no internet connection   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : no internet connection   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:11:41 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:57:34 AM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:11:41 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366302</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital Pharmacy</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:10:44 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:55:22 AM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:10:44 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 15m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -2972,10 +2972,8 @@
           <t>Shankar Gautam</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9801093335</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9801093335</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3010,10 +3008,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.73129</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.73129</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3069,25 +3065,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>CDB382</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.28849</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.28849</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3183,10 +3175,8 @@
           <t>Shankar Gautam</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9801093335</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9801093335</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3221,10 +3211,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.73129</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.73129</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3280,25 +3268,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>CDB382</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.28849</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.28849</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3394,10 +3378,8 @@
           <t>Mega Hospital</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9849670860</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9849670860</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3469,10 +3451,8 @@
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="AH15" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH15" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
@@ -3491,10 +3471,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -3505,7 +3483,7 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : no internet connection   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3601,10 +3579,8 @@
           <t>Mega Hospital Pharmacy</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9862483865</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9862483865</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3676,10 +3652,8 @@
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="AH16" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH16" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
@@ -3698,10 +3672,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -3712,7 +3684,7 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : No internet connection  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3761,7 +3733,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4897,7 +4869,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -4964,7 +4936,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -5031,7 +5003,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Case : no internet connection   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -5098,7 +5070,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : No internet connection  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW16"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -3713,6 +3713,209 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 1:38 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367871</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Dhrubaraj khanal</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Dhrubaraj khanal</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9840794186</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:38:04 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9840794186</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:35:47 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:38:04 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Euro School - Middle school Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>drkhanal1972@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>10:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L33-8</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 2m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3724,7 +3927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3733,7 +3936,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3761,7 +3964,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -3771,7 +3974,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -3782,7 +3985,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.8%</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3997,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 29m</t>
+          <t>4h 11m</t>
         </is>
       </c>
     </row>
@@ -3806,7 +4009,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 26m</t>
+          <t>1d 2h 16m</t>
         </is>
       </c>
     </row>
@@ -3847,10 +4050,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -3973,10 +4176,10 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -5104,6 +5307,73 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367871</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Dhrubaraj khanal</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:38:04 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:35:47 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:38:04 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>1d 2m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -3780,10 +3780,8 @@
           <t>Dhrubaraj khanal</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9840794186</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9840794186</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3873,10 +3871,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -3887,7 +3883,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3936,7 +3932,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5340,7 +5336,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -3912,6 +3912,217 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 3:24 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368039</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Maharjan</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Maharjan</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9802110620</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:57:33 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9802110620</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:57:33 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 03:24:47 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.70138</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Near Mata Devi Oil Store, Sitapaila, Nagarjun , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>dinfrnpal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>09:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.28111</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>23h 27m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>23h 27m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3923,7 +4134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3932,7 +4143,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3960,7 +4171,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -3970,7 +4181,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -3981,7 +4192,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>94.1%</t>
         </is>
       </c>
     </row>
@@ -3993,7 +4204,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 11m</t>
+          <t>5h 23m</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4216,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 16m</t>
+          <t>1d 2h 6m</t>
         </is>
       </c>
     </row>
@@ -4046,10 +4257,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -4172,10 +4383,10 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -5370,6 +5581,73 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368039</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:57:33 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:57:33 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 03:24:47 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>23h 27m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>23h 27m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -3979,10 +3979,8 @@
           <t>Dinesh Maharjan</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9802110620</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9802110620</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4017,10 +4015,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.70138</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.70138</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4076,25 +4072,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.28111</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.28111</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4143,7 +4135,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5614,7 +5606,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW18"/>
+  <dimension ref="A1:AW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -4115,6 +4115,217 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 5:09 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>slow internet issue</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367281</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9841974213</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 05:09:00 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9841974213</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 07:42:47 AM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 05:09:00 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Machhapokhara, Balaju-16,Basantanagar,Nimantrana Guest House &amp; Restaurant,Kathmandu, Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>gautmnavraj@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>17:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB036</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 9h 26m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4126,16 +4337,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4163,7 +4374,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -4173,7 +4384,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -4184,7 +4395,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.4%</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4407,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 23m</t>
+          <t>5h 4m</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4419,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 6m</t>
+          <t>1d 2h 32m</t>
         </is>
       </c>
     </row>
@@ -4303,10 +4514,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -4467,10 +4678,10 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -5640,6 +5851,73 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367281</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 05:09:00 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 07:42:47 AM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 05:09:00 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>1d 9h 26m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_13_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_13_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -4182,10 +4182,8 @@
           <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9841974213</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9841974213</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4220,10 +4218,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4279,25 +4275,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>CDB036</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4346,7 +4338,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5884,7 +5876,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
